--- a/artfynd/A 9268-2023 artfynd.xlsx
+++ b/artfynd/A 9268-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9268-2023 artfynd.xlsx
+++ b/artfynd/A 9268-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,118 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129462820</v>
+      </c>
+      <c r="B3" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Spökberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>663677</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6525510</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Torö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9268-2023 artfynd.xlsx
+++ b/artfynd/A 9268-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107342722</v>
+        <v>107343045</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -725,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663677.3175168007</v>
+        <v>663564</v>
       </c>
       <c r="R2" t="n">
-        <v>6525509.781879072</v>
+        <v>6525524</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -760,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,40 +783,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129462820</v>
+        <v>107342722</v>
       </c>
       <c r="B3" t="n">
-        <v>8450</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Spökberget, Srm</t>
@@ -867,22 +858,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2023-03-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2023-03-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,6 +897,118 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129462820</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Spökberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>663677</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6525510</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Torö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9268-2023 artfynd.xlsx
+++ b/artfynd/A 9268-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107343045</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107342722</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,8 +1024,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129462820</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>